--- a/research/traditional_assets/database/data/ivory_coast/ivory_coast_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/ivory_coast/ivory_coast_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0462</v>
+        <v>0.0687</v>
       </c>
       <c r="E2">
-        <v>0.152</v>
+        <v>0.108</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.3670099722085989</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.3670099722085989</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.2878862187346738</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.2481645031334215</v>
       </c>
       <c r="K2">
-        <v>59.5</v>
+        <v>188.4</v>
       </c>
       <c r="L2">
-        <v>0.5033840947546531</v>
+        <v>0.3079941147621383</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -639,55 +639,61 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.3300055463117027</v>
+        <v>0.2083069787054607</v>
       </c>
       <c r="X2">
-        <v>0.06839092766764372</v>
+        <v>0.0984273094060206</v>
       </c>
       <c r="Y2">
-        <v>0.261614618644059</v>
+        <v>0.1098796692994401</v>
       </c>
       <c r="Z2">
-        <v>0.4248741912293313</v>
+        <v>0.555787752135199</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06423137647574224</v>
+        <v>0.09570690716569695</v>
       </c>
       <c r="AC2">
-        <v>-0.06423137647574224</v>
+        <v>-0.0936868804076894</v>
       </c>
       <c r="AD2">
-        <v>86.3</v>
+        <v>229.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>86.3</v>
+        <v>229.2</v>
       </c>
       <c r="AG2">
-        <v>86.3</v>
+        <v>229.2</v>
       </c>
       <c r="AH2">
-        <v>0.1998610467809171</v>
+        <v>0.1601229565460388</v>
       </c>
       <c r="AI2">
-        <v>0.296767537826685</v>
+        <v>0.2100632389331867</v>
       </c>
       <c r="AJ2">
-        <v>0.1998610467809171</v>
+        <v>0.1601229565460388</v>
       </c>
       <c r="AK2">
-        <v>0.296767537826685</v>
+        <v>0.2100632389331867</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>58.2</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>58.2</v>
+      </c>
+      <c r="AO2">
+        <v>3.025773195876289</v>
+      </c>
+      <c r="AQ2">
+        <v>3.025773195876289</v>
       </c>
     </row>
     <row r="3">
@@ -698,114 +704,358 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Société Générale Côte d'Ivoire - Société Anonyme (BRVM:SGBC)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.147</v>
+      </c>
+      <c r="E3">
+        <v>0.108</v>
+      </c>
+      <c r="G3">
+        <v>0.5942297511911064</v>
+      </c>
+      <c r="H3">
+        <v>0.5942297511911064</v>
+      </c>
+      <c r="I3">
+        <v>0.4661196400211752</v>
+      </c>
+      <c r="J3">
+        <v>0.3953014629535803</v>
+      </c>
+      <c r="K3">
+        <v>98.8</v>
+      </c>
+      <c r="L3">
+        <v>0.2615140285865537</v>
+      </c>
+      <c r="M3">
+        <v>-0</v>
+      </c>
+      <c r="N3">
+        <v>-0</v>
+      </c>
+      <c r="O3">
+        <v>-0</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>-0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0.2083069787054607</v>
+      </c>
+      <c r="X3">
+        <v>0.0984273094060206</v>
+      </c>
+      <c r="Y3">
+        <v>0.1098796692994401</v>
+      </c>
+      <c r="Z3">
+        <v>0.6452604611443211</v>
+      </c>
+      <c r="AA3">
+        <v>0.255072404276452</v>
+      </c>
+      <c r="AB3">
+        <v>0.09570690716569695</v>
+      </c>
+      <c r="AC3">
+        <v>0.159365497110755</v>
+      </c>
+      <c r="AD3">
+        <v>86</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>86</v>
+      </c>
+      <c r="AG3">
+        <v>86</v>
+      </c>
+      <c r="AH3">
+        <v>0.1275775107550808</v>
+      </c>
+      <c r="AI3">
+        <v>0.1616237549332832</v>
+      </c>
+      <c r="AJ3">
+        <v>0.1275775107550808</v>
+      </c>
+      <c r="AK3">
+        <v>0.1616237549332832</v>
+      </c>
+      <c r="AL3">
+        <v>58.2</v>
+      </c>
+      <c r="AM3">
+        <v>58.2</v>
+      </c>
+      <c r="AO3">
+        <v>3.025773195876289</v>
+      </c>
+      <c r="AQ3">
+        <v>3.025773195876289</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ivory Coast</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NSIA Banque Société Anonyme (BRVM:NSBC)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.035</v>
+      </c>
+      <c r="E4">
+        <v>0.0191</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>32</v>
+      </c>
+      <c r="L4">
+        <v>0.2802101576182137</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0.1643554185927067</v>
+      </c>
+      <c r="X4">
+        <v>0.09449295528615649</v>
+      </c>
+      <c r="Y4">
+        <v>0.06986246330655026</v>
+      </c>
+      <c r="Z4">
+        <v>0.5091395452518949</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.0936868804076894</v>
+      </c>
+      <c r="AC4">
+        <v>-0.0936868804076894</v>
+      </c>
+      <c r="AD4">
+        <v>11.7</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>11.7</v>
+      </c>
+      <c r="AG4">
+        <v>11.7</v>
+      </c>
+      <c r="AH4">
+        <v>0.04635499207606973</v>
+      </c>
+      <c r="AI4">
+        <v>0.05053995680345572</v>
+      </c>
+      <c r="AJ4">
+        <v>0.04635499207606973</v>
+      </c>
+      <c r="AK4">
+        <v>0.05053995680345572</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ivory Coast</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Société Ivoirienne de Banque S.A. (BRVM:SIBC)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.0462</v>
-      </c>
-      <c r="E3">
-        <v>0.152</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>59.5</v>
-      </c>
-      <c r="L3">
-        <v>0.5033840947546531</v>
-      </c>
-      <c r="M3">
-        <v>-0</v>
-      </c>
-      <c r="N3">
-        <v>-0</v>
-      </c>
-      <c r="O3">
-        <v>-0</v>
-      </c>
-      <c r="P3">
-        <v>-0</v>
-      </c>
-      <c r="Q3">
-        <v>-0</v>
-      </c>
-      <c r="R3">
-        <v>-0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0.3300055463117027</v>
-      </c>
-      <c r="X3">
-        <v>0.06839092766764372</v>
-      </c>
-      <c r="Y3">
-        <v>0.261614618644059</v>
-      </c>
-      <c r="Z3">
-        <v>0.4248741912293313</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.06423137647574224</v>
-      </c>
-      <c r="AC3">
-        <v>-0.06423137647574224</v>
-      </c>
-      <c r="AD3">
-        <v>86.3</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>86.3</v>
-      </c>
-      <c r="AG3">
-        <v>86.3</v>
-      </c>
-      <c r="AH3">
-        <v>0.1998610467809171</v>
-      </c>
-      <c r="AI3">
-        <v>0.296767537826685</v>
-      </c>
-      <c r="AJ3">
-        <v>0.1998610467809171</v>
-      </c>
-      <c r="AK3">
-        <v>0.296767537826685</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="D5">
+        <v>0.0687</v>
+      </c>
+      <c r="E5">
+        <v>0.134</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>57.6</v>
+      </c>
+      <c r="L5">
+        <v>0.481203007518797</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0.2816625916870416</v>
+      </c>
+      <c r="X5">
+        <v>0.1067266208325195</v>
+      </c>
+      <c r="Y5">
+        <v>0.1749359708545221</v>
+      </c>
+      <c r="Z5">
+        <v>0.4116231086657496</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.09901142378281905</v>
+      </c>
+      <c r="AC5">
+        <v>-0.09901142378281905</v>
+      </c>
+      <c r="AD5">
+        <v>131.5</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>131.5</v>
+      </c>
+      <c r="AG5">
+        <v>131.5</v>
+      </c>
+      <c r="AH5">
+        <v>0.2604476133887899</v>
+      </c>
+      <c r="AI5">
+        <v>0.4015267175572519</v>
+      </c>
+      <c r="AJ5">
+        <v>0.2604476133887899</v>
+      </c>
+      <c r="AK5">
+        <v>0.4015267175572519</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/ivory_coast/ivory_coast_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/ivory_coast/ivory_coast_bank_money_center.xlsx
@@ -591,25 +591,25 @@
         <v>0.0687</v>
       </c>
       <c r="E2">
-        <v>0.108</v>
+        <v>0.19</v>
       </c>
       <c r="G2">
-        <v>0.3670099722085989</v>
+        <v>0.3120976394849785</v>
       </c>
       <c r="H2">
-        <v>0.3670099722085989</v>
+        <v>0.3120976394849785</v>
       </c>
       <c r="I2">
-        <v>0.2878862187346738</v>
+        <v>0.3412017167381974</v>
       </c>
       <c r="J2">
-        <v>0.2481645031334215</v>
+        <v>0.2942895572773332</v>
       </c>
       <c r="K2">
-        <v>188.4</v>
+        <v>267.1</v>
       </c>
       <c r="L2">
-        <v>0.3079941147621383</v>
+        <v>0.3582349785407726</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -639,61 +639,61 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.2083069787054607</v>
+        <v>0.2738095238095238</v>
       </c>
       <c r="X2">
-        <v>0.0984273094060206</v>
+        <v>0.08039411443804892</v>
       </c>
       <c r="Y2">
-        <v>0.1098796692994401</v>
+        <v>0.1934154093714749</v>
       </c>
       <c r="Z2">
-        <v>0.555787752135199</v>
+        <v>1.802707930367505</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.09570690716569695</v>
+        <v>0.07944641297524502</v>
       </c>
       <c r="AC2">
-        <v>-0.0936868804076894</v>
+        <v>-0.07761237952040308</v>
       </c>
       <c r="AD2">
-        <v>229.2</v>
+        <v>244.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>229.2</v>
+        <v>244.1</v>
       </c>
       <c r="AG2">
-        <v>229.2</v>
+        <v>244.1</v>
       </c>
       <c r="AH2">
-        <v>0.1601229565460388</v>
+        <v>0.1366511784134804</v>
       </c>
       <c r="AI2">
-        <v>0.2100632389331867</v>
+        <v>0.2252052772395977</v>
       </c>
       <c r="AJ2">
-        <v>0.1601229565460388</v>
+        <v>0.1366511784134804</v>
       </c>
       <c r="AK2">
-        <v>0.2100632389331867</v>
+        <v>0.2252052772395977</v>
       </c>
       <c r="AL2">
-        <v>58.2</v>
+        <v>69</v>
       </c>
       <c r="AM2">
-        <v>58.2</v>
+        <v>69</v>
       </c>
       <c r="AO2">
-        <v>3.025773195876289</v>
+        <v>3.68695652173913</v>
       </c>
       <c r="AQ2">
-        <v>3.025773195876289</v>
+        <v>3.68695652173913</v>
       </c>
     </row>
     <row r="3">
@@ -713,28 +713,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.147</v>
+        <v>0.119</v>
       </c>
       <c r="E3">
-        <v>0.108</v>
+        <v>0.19</v>
       </c>
       <c r="G3">
-        <v>0.5942297511911064</v>
+        <v>0.4869219501987864</v>
       </c>
       <c r="H3">
-        <v>0.5942297511911064</v>
+        <v>0.4869219501987864</v>
       </c>
       <c r="I3">
-        <v>0.4661196400211752</v>
+        <v>0.5323289391086001</v>
       </c>
       <c r="J3">
-        <v>0.3953014629535803</v>
+        <v>0.4333904592635631</v>
       </c>
       <c r="K3">
-        <v>98.8</v>
+        <v>152</v>
       </c>
       <c r="L3">
-        <v>0.2615140285865537</v>
+        <v>0.3180581711655158</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -763,62 +763,47 @@
       <c r="V3">
         <v>0</v>
       </c>
-      <c r="W3">
-        <v>0.2083069787054607</v>
-      </c>
       <c r="X3">
-        <v>0.0984273094060206</v>
-      </c>
-      <c r="Y3">
-        <v>0.1098796692994401</v>
-      </c>
-      <c r="Z3">
-        <v>0.6452604611443211</v>
-      </c>
-      <c r="AA3">
-        <v>0.255072404276452</v>
+        <v>0.08523047374169446</v>
       </c>
       <c r="AB3">
-        <v>0.09570690716569695</v>
-      </c>
-      <c r="AC3">
-        <v>0.159365497110755</v>
+        <v>0.08197368312194542</v>
       </c>
       <c r="AD3">
-        <v>86</v>
+        <v>220.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>86</v>
+        <v>220.2</v>
       </c>
       <c r="AG3">
-        <v>86</v>
+        <v>220.2</v>
       </c>
       <c r="AH3">
-        <v>0.1275775107550808</v>
+        <v>0.2074227581009797</v>
       </c>
       <c r="AI3">
-        <v>0.1616237549332832</v>
+        <v>0.2798322531452535</v>
       </c>
       <c r="AJ3">
-        <v>0.1275775107550808</v>
+        <v>0.2074227581009797</v>
       </c>
       <c r="AK3">
-        <v>0.1616237549332832</v>
+        <v>0.2798322531452535</v>
       </c>
       <c r="AL3">
-        <v>58.2</v>
+        <v>69</v>
       </c>
       <c r="AM3">
-        <v>58.2</v>
+        <v>69</v>
       </c>
       <c r="AO3">
-        <v>3.025773195876289</v>
+        <v>3.68695652173913</v>
       </c>
       <c r="AQ3">
-        <v>3.025773195876289</v>
+        <v>3.68695652173913</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +814,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NSIA Banque Société Anonyme (BRVM:NSBC)</t>
+          <t>Société Ivoirienne de Banque S.A. (BRVM:SIBC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,10 +823,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.035</v>
+        <v>0.0687</v>
       </c>
       <c r="E4">
-        <v>0.0191</v>
+        <v>0.134</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,10 +841,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>32</v>
+        <v>57.6</v>
       </c>
       <c r="L4">
-        <v>0.2802101576182137</v>
+        <v>0.481203007518797</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -889,49 +874,43 @@
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0.1643554185927067</v>
+        <v>0.253968253968254</v>
       </c>
       <c r="X4">
-        <v>0.09449295528615649</v>
+        <v>0.07761237952040308</v>
       </c>
       <c r="Y4">
-        <v>0.06986246330655026</v>
+        <v>0.1763558744478509</v>
       </c>
       <c r="Z4">
-        <v>0.5091395452518949</v>
+        <v>0.6329984135378105</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0936868804076894</v>
+        <v>0.07761237952040308</v>
       </c>
       <c r="AC4">
-        <v>-0.0936868804076894</v>
+        <v>-0.07761237952040308</v>
       </c>
       <c r="AD4">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>0.04635499207606973</v>
-      </c>
-      <c r="AI4">
-        <v>0.05053995680345572</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.04635499207606973</v>
-      </c>
-      <c r="AK4">
-        <v>0.05053995680345572</v>
+        <v>0</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +927,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Société Ivoirienne de Banque S.A. (BRVM:SIBC)</t>
+          <t>NSIA Banque Société Anonyme (BRVM:NSBC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,10 +936,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0687</v>
+        <v>-0.0602</v>
       </c>
       <c r="E5">
-        <v>0.134</v>
+        <v>0.208</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,10 +954,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>57.6</v>
+        <v>57.5</v>
       </c>
       <c r="L5">
-        <v>0.481203007518797</v>
+        <v>0.3885135135135135</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1008,49 +987,49 @@
         <v>0</v>
       </c>
       <c r="W5">
-        <v>0.2816625916870416</v>
+        <v>0.2738095238095238</v>
       </c>
       <c r="X5">
-        <v>0.1067266208325195</v>
+        <v>0.08039411443804892</v>
       </c>
       <c r="Y5">
-        <v>0.1749359708545221</v>
+        <v>0.1934154093714749</v>
       </c>
       <c r="Z5">
-        <v>0.4116231086657496</v>
+        <v>0.6592427616926503</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.09901142378281905</v>
+        <v>0.07944641297524502</v>
       </c>
       <c r="AC5">
-        <v>-0.09901142378281905</v>
+        <v>-0.07944641297524502</v>
       </c>
       <c r="AD5">
-        <v>131.5</v>
+        <v>23.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>131.5</v>
+        <v>23.9</v>
       </c>
       <c r="AG5">
-        <v>131.5</v>
+        <v>23.9</v>
       </c>
       <c r="AH5">
-        <v>0.2604476133887899</v>
+        <v>0.08722627737226277</v>
       </c>
       <c r="AI5">
-        <v>0.4015267175572519</v>
+        <v>0.08047138047138047</v>
       </c>
       <c r="AJ5">
-        <v>0.2604476133887899</v>
+        <v>0.08722627737226277</v>
       </c>
       <c r="AK5">
-        <v>0.4015267175572519</v>
+        <v>0.08047138047138047</v>
       </c>
       <c r="AL5">
         <v>0</v>
